--- a/tests/fixtures/xlsx/racesense-sample-league.xlsx
+++ b/tests/fixtures/xlsx/racesense-sample-league.xlsx
@@ -152,7 +152,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:25</t>
+          <t xml:space="preserve">18:55</t>
         </is>
       </c>
     </row>
@@ -216,55 +216,55 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7887</t>
+          <t xml:space="preserve">IRL3429</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3429</t>
+          <t xml:space="preserve">IRL32032</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2237</t>
+          <t xml:space="preserve">IRL7887</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL32032</t>
+          <t xml:space="preserve">IRL2237</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
@@ -276,91 +276,91 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4470</t>
+          <t xml:space="preserve">IRL9855</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9855</t>
+          <t xml:space="preserve">IRL2240</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR4947R</t>
+          <t xml:space="preserve">IRL4076</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4076</t>
+          <t xml:space="preserve">FRA78</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL35950</t>
+          <t xml:space="preserve">IRL4475</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2240</t>
+          <t xml:space="preserve">GBR4947R</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRA78</t>
+          <t xml:space="preserve">IRL35950</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
@@ -372,187 +372,187 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4475</t>
+          <t xml:space="preserve">IRL4470</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1759</t>
+          <t xml:space="preserve">IRL3214</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9216</t>
+          <t xml:space="preserve">IRL985</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">KZ3494</t>
+          <t xml:space="preserve">IRL3330</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3330</t>
+          <t xml:space="preserve">IRL1551</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3300</t>
+          <t xml:space="preserve">IRL9216</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9202</t>
+          <t xml:space="preserve">IRL5435</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9992</t>
+          <t xml:space="preserve">IRL33301</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3214</t>
+          <t xml:space="preserve">IRL1333</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1551</t>
+          <t xml:space="preserve">IRL1759</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1333</t>
+          <t xml:space="preserve">IRL9978</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9978</t>
+          <t xml:space="preserve">IRL9992</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL33301</t>
+          <t xml:space="preserve">KZ3494</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5435</t>
+          <t xml:space="preserve">IRL3300</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL985</t>
+          <t xml:space="preserve">IRL9202</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
@@ -576,14 +576,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5499Y</t>
+          <t xml:space="preserve">IRL2480</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -595,43 +595,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5333</t>
+          <t xml:space="preserve">1192C</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL8044</t>
+          <t xml:space="preserve">GK149</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR6095T</t>
+          <t xml:space="preserve">5499Y</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192C</t>
+          <t xml:space="preserve">IRL8044</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -643,19 +643,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">U4</t>
+          <t xml:space="preserve">IRL5333</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2480</t>
+          <t xml:space="preserve">148</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -672,79 +672,79 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GK149</t>
+          <t xml:space="preserve">GBR6095T</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1844</t>
+          <t xml:space="preserve">IRL2840</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">IRL1844</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL21</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2840</t>
+          <t xml:space="preserve">U4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">148</t>
+          <t xml:space="preserve">IRL21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">41:00.000</t>
+          <t xml:space="preserve">37:33.000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:30:00.000</t>
+          <t xml:space="preserve">19:37:33.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -834,17 +834,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7887</t>
+          <t xml:space="preserve">IRL3429</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">41:47.070</t>
+          <t xml:space="preserve">40:53.170</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:30:47.130</t>
+          <t xml:space="preserve">19:40:53.170</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.210</t>
+          <t xml:space="preserve">9.205</t>
         </is>
       </c>
     </row>
@@ -866,17 +866,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3429</t>
+          <t xml:space="preserve">IRL32032</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">42:34.140</t>
+          <t xml:space="preserve">42:13.340</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:31:34.260</t>
+          <t xml:space="preserve">19:42:13.340</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.220</t>
+          <t xml:space="preserve">9.210</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2237</t>
+          <t xml:space="preserve">IRL7887</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">43:21.210</t>
+          <t xml:space="preserve">42:20.510</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:32:21.390</t>
+          <t xml:space="preserve">19:42:20.510</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.230</t>
+          <t xml:space="preserve">9.215</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL32032</t>
+          <t xml:space="preserve">IRL2237</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">44:08.280</t>
+          <t xml:space="preserve">42:51.680</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:33:08.520</t>
+          <t xml:space="preserve">19:42:51.680</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.240</t>
+          <t xml:space="preserve">9.220</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">44:55.350</t>
+          <t xml:space="preserve">44:31.850</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:33:55.650</t>
+          <t xml:space="preserve">19:44:31.850</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.250</t>
+          <t xml:space="preserve">9.225</t>
         </is>
       </c>
     </row>
@@ -994,17 +994,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4470</t>
+          <t xml:space="preserve">IRL9855</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">45:42.420</t>
+          <t xml:space="preserve">45:19.020</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:34:42.780</t>
+          <t xml:space="preserve">19:45:19.020</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.260</t>
+          <t xml:space="preserve">9.230</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9855</t>
+          <t xml:space="preserve">IRL2240</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">46:29.490</t>
+          <t xml:space="preserve">45:46.190</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:35:29.910</t>
+          <t xml:space="preserve">19:45:46.190</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.270</t>
+          <t xml:space="preserve">9.235</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR4947R</t>
+          <t xml:space="preserve">IRL4076</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">47:16.560</t>
+          <t xml:space="preserve">46:33.360</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:36:16.040</t>
+          <t xml:space="preserve">19:46:33.360</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.280</t>
+          <t xml:space="preserve">9.240</t>
         </is>
       </c>
     </row>
@@ -1090,17 +1090,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4076</t>
+          <t xml:space="preserve">FRA78</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">48:03.630</t>
+          <t xml:space="preserve">46:37.530</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:37:03.170</t>
+          <t xml:space="preserve">19:46:37.530</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.290</t>
+          <t xml:space="preserve">9.245</t>
         </is>
       </c>
     </row>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL35950</t>
+          <t xml:space="preserve">IRL4475</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">48:50.700</t>
+          <t xml:space="preserve">46:37.700</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:37:50.300</t>
+          <t xml:space="preserve">19:46:37.700</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.300</t>
+          <t xml:space="preserve">9.250</t>
         </is>
       </c>
     </row>
@@ -1154,17 +1154,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2240</t>
+          <t xml:space="preserve">GBR4947R</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">49:37.770</t>
+          <t xml:space="preserve">46:50.870</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:38:37.430</t>
+          <t xml:space="preserve">19:46:50.870</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.310</t>
+          <t xml:space="preserve">9.255</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1186,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRA78</t>
+          <t xml:space="preserve">IRL35950</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">50:24.840</t>
+          <t xml:space="preserve">47:03.040</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:39:24.560</t>
+          <t xml:space="preserve">19:47:03.040</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.320</t>
+          <t xml:space="preserve">9.260</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">51:11.910</t>
+          <t xml:space="preserve">47:15.210</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:40:11.690</t>
+          <t xml:space="preserve">19:47:15.210</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.330</t>
+          <t xml:space="preserve">9.265</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4475</t>
+          <t xml:space="preserve">IRL4470</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">51:58.980</t>
+          <t xml:space="preserve">48:23.380</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:40:58.820</t>
+          <t xml:space="preserve">19:48:23.380</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.340</t>
+          <t xml:space="preserve">9.270</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1759</t>
+          <t xml:space="preserve">IRL3214</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">52:45.050</t>
+          <t xml:space="preserve">56:31.550</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:41:45.950</t>
+          <t xml:space="preserve">19:56:31.550</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.350</t>
+          <t xml:space="preserve">9.275</t>
         </is>
       </c>
     </row>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9216</t>
+          <t xml:space="preserve">IRL985</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">53:32.120</t>
+          <t xml:space="preserve">56:41.720</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:42:32.080</t>
+          <t xml:space="preserve">19:56:41.720</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.360</t>
+          <t xml:space="preserve">9.280</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">KZ3494</t>
+          <t xml:space="preserve">IRL3330</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">54:19.190</t>
+          <t xml:space="preserve">57:05.890</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:43:19.210</t>
+          <t xml:space="preserve">19:57:05.890</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.370</t>
+          <t xml:space="preserve">9.285</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3330</t>
+          <t xml:space="preserve">IRL1551</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">55:06.260</t>
+          <t xml:space="preserve">57:23.060</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:44:06.340</t>
+          <t xml:space="preserve">19:57:23.060</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.380</t>
+          <t xml:space="preserve">9.290</t>
         </is>
       </c>
     </row>
@@ -1410,17 +1410,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3300</t>
+          <t xml:space="preserve">IRL9216</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">55:53.330</t>
+          <t xml:space="preserve">57:42.230</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:44:53.470</t>
+          <t xml:space="preserve">19:57:42.230</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.390</t>
+          <t xml:space="preserve">9.295</t>
         </is>
       </c>
     </row>
@@ -1442,17 +1442,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9202</t>
+          <t xml:space="preserve">IRL5435</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">56:40.400</t>
+          <t xml:space="preserve">57:51.400</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:45:40.600</t>
+          <t xml:space="preserve">19:57:51.400</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.400</t>
+          <t xml:space="preserve">9.300</t>
         </is>
       </c>
     </row>
@@ -1474,17 +1474,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9992</t>
+          <t xml:space="preserve">IRL33301</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">57:27.470</t>
+          <t xml:space="preserve">58:12.570</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:46:27.730</t>
+          <t xml:space="preserve">19:58:12.570</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.410</t>
+          <t xml:space="preserve">9.305</t>
         </is>
       </c>
     </row>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3214</t>
+          <t xml:space="preserve">IRL1333</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">58:14.540</t>
+          <t xml:space="preserve">58:19.740</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:47:14.860</t>
+          <t xml:space="preserve">19:58:19.740</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.420</t>
+          <t xml:space="preserve">9.310</t>
         </is>
       </c>
     </row>
@@ -1538,17 +1538,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1551</t>
+          <t xml:space="preserve">IRL1759</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">59:01.610</t>
+          <t xml:space="preserve">58:21.910</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:48:01.990</t>
+          <t xml:space="preserve">19:58:21.910</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.430</t>
+          <t xml:space="preserve">9.315</t>
         </is>
       </c>
     </row>
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1333</t>
+          <t xml:space="preserve">IRL9978</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">59:48.680</t>
+          <t xml:space="preserve">58:31.080</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:48:48.120</t>
+          <t xml:space="preserve">19:58:31.080</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.440</t>
+          <t xml:space="preserve">9.320</t>
         </is>
       </c>
     </row>
@@ -1602,17 +1602,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9978</t>
+          <t xml:space="preserve">IRL9992</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">60:35.750</t>
+          <t xml:space="preserve">58:51.250</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:49:35.250</t>
+          <t xml:space="preserve">19:58:51.250</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.450</t>
+          <t xml:space="preserve">9.325</t>
         </is>
       </c>
     </row>
@@ -1634,17 +1634,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL33301</t>
+          <t xml:space="preserve">KZ3494</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">61:22.820</t>
+          <t xml:space="preserve">58:54.420</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:50:22.380</t>
+          <t xml:space="preserve">19:58:54.420</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.460</t>
+          <t xml:space="preserve">9.330</t>
         </is>
       </c>
     </row>
@@ -1666,17 +1666,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5435</t>
+          <t xml:space="preserve">IRL3300</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">62:09.890</t>
+          <t xml:space="preserve">59:00.590</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:51:09.510</t>
+          <t xml:space="preserve">19:59:00.590</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.470</t>
+          <t xml:space="preserve">9.335</t>
         </is>
       </c>
     </row>
@@ -1698,17 +1698,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL985</t>
+          <t xml:space="preserve">IRL9202</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">62:56.960</t>
+          <t xml:space="preserve">59:44.760</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:51:56.640</t>
+          <t xml:space="preserve">19:59:44.760</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.480</t>
+          <t xml:space="preserve">9.340</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">63:43.030</t>
+          <t xml:space="preserve">59:56.930</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:52:43.770</t>
+          <t xml:space="preserve">19:59:56.930</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.490</t>
+          <t xml:space="preserve">9.345</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">64:30.100</t>
+          <t xml:space="preserve">65:55.100</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:53:30.900</t>
+          <t xml:space="preserve">20:05:55.100</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.500</t>
+          <t xml:space="preserve">9.350</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5499Y</t>
+          <t xml:space="preserve">IRL2480</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">65:17.170</t>
+          <t xml:space="preserve">67:23.270</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:54:17.030</t>
+          <t xml:space="preserve">20:07:23.270</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.510</t>
+          <t xml:space="preserve">9.355</t>
         </is>
       </c>
     </row>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5333</t>
+          <t xml:space="preserve">1192C</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">66:04.240</t>
+          <t xml:space="preserve">67:41.440</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:55:04.160</t>
+          <t xml:space="preserve">20:07:41.440</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.520</t>
+          <t xml:space="preserve">9.360</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL8044</t>
+          <t xml:space="preserve">GK149</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">66:51.310</t>
+          <t xml:space="preserve">68:45.610</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:55:51.290</t>
+          <t xml:space="preserve">20:08:45.610</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.530</t>
+          <t xml:space="preserve">9.365</t>
         </is>
       </c>
     </row>
@@ -1890,17 +1890,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR6095T</t>
+          <t xml:space="preserve">5499Y</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">67:38.380</t>
+          <t xml:space="preserve">69:36.780</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:56:38.420</t>
+          <t xml:space="preserve">20:09:36.780</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.540</t>
+          <t xml:space="preserve">9.370</t>
         </is>
       </c>
     </row>
@@ -1922,17 +1922,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192C</t>
+          <t xml:space="preserve">IRL8044</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">68:25.450</t>
+          <t xml:space="preserve">69:53.950</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:57:25.550</t>
+          <t xml:space="preserve">20:09:53.950</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.550</t>
+          <t xml:space="preserve">9.375</t>
         </is>
       </c>
     </row>
@@ -1954,17 +1954,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">U4</t>
+          <t xml:space="preserve">IRL5333</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">69:12.520</t>
+          <t xml:space="preserve">70:02.120</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:58:12.680</t>
+          <t xml:space="preserve">20:10:02.120</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.560</t>
+          <t xml:space="preserve">9.380</t>
         </is>
       </c>
     </row>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2480</t>
+          <t xml:space="preserve">148</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">69:59.590</t>
+          <t xml:space="preserve">70:35.290</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:58:59.810</t>
+          <t xml:space="preserve">20:10:35.290</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.570</t>
+          <t xml:space="preserve">9.385</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">70:46.660</t>
+          <t xml:space="preserve">70:49.460</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:59:46.940</t>
+          <t xml:space="preserve">20:10:49.460</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.580</t>
+          <t xml:space="preserve">9.390</t>
         </is>
       </c>
     </row>
@@ -2050,17 +2050,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">GK149</t>
+          <t xml:space="preserve">GBR6095T</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">71:33.730</t>
+          <t xml:space="preserve">71:04.630</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:00:33.070</t>
+          <t xml:space="preserve">20:11:04.630</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.590</t>
+          <t xml:space="preserve">9.395</t>
         </is>
       </c>
     </row>
@@ -2082,17 +2082,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1844</t>
+          <t xml:space="preserve">IRL2840</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">72:20.800</t>
+          <t xml:space="preserve">71:54.800</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:01:20.200</t>
+          <t xml:space="preserve">20:11:54.800</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.600</t>
+          <t xml:space="preserve">9.400</t>
         </is>
       </c>
     </row>
@@ -2114,17 +2114,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">IRL1844</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">73:07.870</t>
+          <t xml:space="preserve">71:57.970</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:02:07.330</t>
+          <t xml:space="preserve">20:11:57.970</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.610</t>
+          <t xml:space="preserve">9.405</t>
         </is>
       </c>
     </row>
@@ -2146,17 +2146,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL21</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">73:54.940</t>
+          <t xml:space="preserve">72:22.140</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:02:54.460</t>
+          <t xml:space="preserve">20:12:22.140</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -2166,61 +2166,71 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.620</t>
+          <t xml:space="preserve">9.410</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">44.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2840</t>
+          <t xml:space="preserve">U4</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">72:51.310</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">20:12:51.310</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">9.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.415</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">45.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">148</t>
+          <t xml:space="preserve">IRL21</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">74:15.480</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">20:14:15.480</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">6.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.420</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2350,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:27</t>
+          <t xml:space="preserve">18:55</t>
         </is>
       </c>
     </row>
@@ -2399,72 +2409,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL35950</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCS</t>
+          <t xml:space="preserve">IRL2046</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-14.30</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9855</t>
+          <t xml:space="preserve">IRL7887</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR4947R</t>
+          <t xml:space="preserve">IRL3429</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4076</t>
+          <t xml:space="preserve">IRL32032</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2240</t>
+          <t xml:space="preserve">IRL7404</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRA78</t>
+          <t xml:space="preserve">IRL2240</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2481,50 +2486,50 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4475</t>
+          <t xml:space="preserve">FRA78</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1759</t>
+          <t xml:space="preserve">IRL4076</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9216</t>
+          <t xml:space="preserve">IRL9855</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">KZ3494</t>
+          <t xml:space="preserve">GBR4947R</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2536,108 +2541,108 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3330</t>
+          <t xml:space="preserve">IRL4470</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3300</t>
+          <t xml:space="preserve">IRL35950</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9202</t>
+          <t xml:space="preserve">IRL4475</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9992</t>
+          <t xml:space="preserve">IRL9216</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3214</t>
+          <t xml:space="preserve">IRL1551</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1551</t>
+          <t xml:space="preserve">IRL3330</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1333</t>
+          <t xml:space="preserve">IRL985</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9978</t>
+          <t xml:space="preserve">IRL1333</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL33301</t>
+          <t xml:space="preserve">IRL9202</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
@@ -2649,50 +2654,50 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL985</t>
+          <t xml:space="preserve">IRL3300</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3276</t>
+          <t xml:space="preserve">KZ3494</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITA10767</t>
+          <t xml:space="preserve">IRL9992</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5499Y</t>
+          <t xml:space="preserve">IRL9978</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2704,43 +2709,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5333</t>
+          <t xml:space="preserve">IRL3214</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL8044</t>
+          <t xml:space="preserve">IRL1759</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR6095T</t>
+          <t xml:space="preserve">IRL33301</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192C</t>
+          <t xml:space="preserve">IRL3276</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2752,12 +2757,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">U4</t>
+          <t xml:space="preserve">ITA10767</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
@@ -2769,26 +2774,26 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL216</t>
+          <t xml:space="preserve">1192C</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GK149</t>
+          <t xml:space="preserve">IRL5333</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2800,48 +2805,48 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1844</t>
+          <t xml:space="preserve">GK149</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">IRL8044</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL21</t>
+          <t xml:space="preserve">U4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2840</t>
+          <t xml:space="preserve">5499Y</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
@@ -2853,91 +2858,91 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">4.00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2046</t>
+          <t xml:space="preserve">GBR6095T</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7887</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3429</t>
+          <t xml:space="preserve">IRL216</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2237</t>
+          <t xml:space="preserve">IRL1844</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL32032</t>
+          <t xml:space="preserve">IRL21</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7404</t>
+          <t xml:space="preserve">IRL2840</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4470</t>
+          <t xml:space="preserve">IRL2237</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
@@ -2995,17 +3000,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9855</t>
+          <t xml:space="preserve">IRL2046</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">41:00.000</t>
+          <t xml:space="preserve">38:43.000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:35:00.000</t>
+          <t xml:space="preserve">19:38:43.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3027,17 +3032,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR4947R</t>
+          <t xml:space="preserve">IRL7887</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">41:47.070</t>
+          <t xml:space="preserve">41:33.170</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:35:47.130</t>
+          <t xml:space="preserve">19:41:33.170</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3047,7 +3052,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.210</t>
+          <t xml:space="preserve">9.205</t>
         </is>
       </c>
     </row>
@@ -3059,17 +3064,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4076</t>
+          <t xml:space="preserve">IRL3429</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">42:34.140</t>
+          <t xml:space="preserve">42:24.340</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:36:34.260</t>
+          <t xml:space="preserve">19:42:24.340</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3079,7 +3084,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.220</t>
+          <t xml:space="preserve">9.210</t>
         </is>
       </c>
     </row>
@@ -3091,17 +3096,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL35950</t>
+          <t xml:space="preserve">IRL32032</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">43:21.210</t>
+          <t xml:space="preserve">42:37.510</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:37:21.390</t>
+          <t xml:space="preserve">19:42:37.510</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3111,7 +3116,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.230</t>
+          <t xml:space="preserve">9.215</t>
         </is>
       </c>
     </row>
@@ -3123,17 +3128,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2240</t>
+          <t xml:space="preserve">IRL7404</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">44:08.280</t>
+          <t xml:space="preserve">44:28.680</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:38:08.520</t>
+          <t xml:space="preserve">19:44:28.680</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3143,7 +3148,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.240</t>
+          <t xml:space="preserve">9.220</t>
         </is>
       </c>
     </row>
@@ -3155,17 +3160,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRA78</t>
+          <t xml:space="preserve">IRL2240</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">44:55.350</t>
+          <t xml:space="preserve">45:03.850</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:38:55.650</t>
+          <t xml:space="preserve">19:45:03.850</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3175,7 +3180,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.250</t>
+          <t xml:space="preserve">9.225</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3197,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">45:42.420</t>
+          <t xml:space="preserve">45:28.020</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:39:42.780</t>
+          <t xml:space="preserve">19:45:28.020</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3207,7 +3212,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.260</t>
+          <t xml:space="preserve">9.230</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3224,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4475</t>
+          <t xml:space="preserve">FRA78</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">46:29.490</t>
+          <t xml:space="preserve">45:52.190</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:40:29.910</t>
+          <t xml:space="preserve">19:45:52.190</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3239,7 +3244,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.270</t>
+          <t xml:space="preserve">9.235</t>
         </is>
       </c>
     </row>
@@ -3251,17 +3256,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1759</t>
+          <t xml:space="preserve">IRL4076</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">47:16.560</t>
+          <t xml:space="preserve">46:11.360</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:41:16.040</t>
+          <t xml:space="preserve">19:46:11.360</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3271,7 +3276,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.280</t>
+          <t xml:space="preserve">9.240</t>
         </is>
       </c>
     </row>
@@ -3283,17 +3288,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9216</t>
+          <t xml:space="preserve">IRL9855</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">48:03.630</t>
+          <t xml:space="preserve">46:20.530</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:42:03.170</t>
+          <t xml:space="preserve">19:46:20.530</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3303,7 +3308,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.290</t>
+          <t xml:space="preserve">9.245</t>
         </is>
       </c>
     </row>
@@ -3315,17 +3320,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">KZ3494</t>
+          <t xml:space="preserve">GBR4947R</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">48:50.700</t>
+          <t xml:space="preserve">47:22.700</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:42:50.300</t>
+          <t xml:space="preserve">19:47:22.700</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3335,7 +3340,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.300</t>
+          <t xml:space="preserve">9.250</t>
         </is>
       </c>
     </row>
@@ -3347,17 +3352,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3330</t>
+          <t xml:space="preserve">IRL4470</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">49:37.770</t>
+          <t xml:space="preserve">47:28.870</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:43:37.430</t>
+          <t xml:space="preserve">19:47:28.870</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3367,7 +3372,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.310</t>
+          <t xml:space="preserve">9.255</t>
         </is>
       </c>
     </row>
@@ -3379,17 +3384,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3300</t>
+          <t xml:space="preserve">IRL35950</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">50:24.840</t>
+          <t xml:space="preserve">47:40.040</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:44:24.560</t>
+          <t xml:space="preserve">19:47:40.040</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3399,7 +3404,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.320</t>
+          <t xml:space="preserve">9.260</t>
         </is>
       </c>
     </row>
@@ -3411,17 +3416,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9202</t>
+          <t xml:space="preserve">IRL4475</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">51:11.910</t>
+          <t xml:space="preserve">47:53.210</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:45:11.690</t>
+          <t xml:space="preserve">19:47:53.210</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3431,7 +3436,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.330</t>
+          <t xml:space="preserve">9.265</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3448,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9992</t>
+          <t xml:space="preserve">IRL9216</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">51:58.980</t>
+          <t xml:space="preserve">56:34.380</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:45:58.820</t>
+          <t xml:space="preserve">19:56:34.380</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3463,7 +3468,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.340</t>
+          <t xml:space="preserve">9.270</t>
         </is>
       </c>
     </row>
@@ -3475,17 +3480,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3214</t>
+          <t xml:space="preserve">IRL1551</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">52:45.050</t>
+          <t xml:space="preserve">57:14.550</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:46:45.950</t>
+          <t xml:space="preserve">19:57:14.550</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3495,7 +3500,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.350</t>
+          <t xml:space="preserve">9.275</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3512,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1551</t>
+          <t xml:space="preserve">IRL3330</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">53:32.120</t>
+          <t xml:space="preserve">57:22.720</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:47:32.080</t>
+          <t xml:space="preserve">19:57:22.720</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3527,7 +3532,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.360</t>
+          <t xml:space="preserve">9.280</t>
         </is>
       </c>
     </row>
@@ -3539,17 +3544,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1333</t>
+          <t xml:space="preserve">IRL985</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">54:19.190</t>
+          <t xml:space="preserve">57:24.890</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:48:19.210</t>
+          <t xml:space="preserve">19:57:24.890</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3559,7 +3564,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.370</t>
+          <t xml:space="preserve">9.285</t>
         </is>
       </c>
     </row>
@@ -3571,17 +3576,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9978</t>
+          <t xml:space="preserve">IRL1333</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">55:06.260</t>
+          <t xml:space="preserve">57:32.060</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:49:06.340</t>
+          <t xml:space="preserve">19:57:32.060</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3591,7 +3596,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.380</t>
+          <t xml:space="preserve">9.290</t>
         </is>
       </c>
     </row>
@@ -3603,17 +3608,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL33301</t>
+          <t xml:space="preserve">IRL9202</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">55:53.330</t>
+          <t xml:space="preserve">57:41.230</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:49:53.470</t>
+          <t xml:space="preserve">19:57:41.230</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3623,7 +3628,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.390</t>
+          <t xml:space="preserve">9.295</t>
         </is>
       </c>
     </row>
@@ -3640,12 +3645,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">56:40.400</t>
+          <t xml:space="preserve">57:41.400</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:50:40.600</t>
+          <t xml:space="preserve">19:57:41.400</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3655,7 +3660,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.400</t>
+          <t xml:space="preserve">9.300</t>
         </is>
       </c>
     </row>
@@ -3667,17 +3672,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL985</t>
+          <t xml:space="preserve">IRL3300</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">57:27.470</t>
+          <t xml:space="preserve">58:16.570</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:51:27.730</t>
+          <t xml:space="preserve">19:58:16.570</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3687,7 +3692,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.410</t>
+          <t xml:space="preserve">9.305</t>
         </is>
       </c>
     </row>
@@ -3699,17 +3704,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3276</t>
+          <t xml:space="preserve">KZ3494</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">58:14.540</t>
+          <t xml:space="preserve">58:29.740</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:52:14.860</t>
+          <t xml:space="preserve">19:58:29.740</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3719,7 +3724,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.420</t>
+          <t xml:space="preserve">9.310</t>
         </is>
       </c>
     </row>
@@ -3731,17 +3736,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITA10767</t>
+          <t xml:space="preserve">IRL9992</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">59:01.610</t>
+          <t xml:space="preserve">59:01.910</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:53:01.990</t>
+          <t xml:space="preserve">19:59:01.910</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3751,7 +3756,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.430</t>
+          <t xml:space="preserve">9.315</t>
         </is>
       </c>
     </row>
@@ -3763,17 +3768,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5499Y</t>
+          <t xml:space="preserve">IRL9978</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">59:48.680</t>
+          <t xml:space="preserve">59:17.080</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:53:48.120</t>
+          <t xml:space="preserve">19:59:17.080</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3783,7 +3788,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.440</t>
+          <t xml:space="preserve">9.320</t>
         </is>
       </c>
     </row>
@@ -3795,17 +3800,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5333</t>
+          <t xml:space="preserve">IRL3214</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">60:35.750</t>
+          <t xml:space="preserve">59:29.250</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:54:35.250</t>
+          <t xml:space="preserve">19:59:29.250</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3815,7 +3820,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.450</t>
+          <t xml:space="preserve">9.325</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3832,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL8044</t>
+          <t xml:space="preserve">IRL1759</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">61:22.820</t>
+          <t xml:space="preserve">59:50.420</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:55:22.380</t>
+          <t xml:space="preserve">19:59:50.420</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3847,7 +3852,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.460</t>
+          <t xml:space="preserve">9.330</t>
         </is>
       </c>
     </row>
@@ -3859,17 +3864,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR6095T</t>
+          <t xml:space="preserve">IRL33301</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">62:09.890</t>
+          <t xml:space="preserve">60:16.590</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:56:09.510</t>
+          <t xml:space="preserve">20:00:16.590</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3879,7 +3884,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.470</t>
+          <t xml:space="preserve">9.335</t>
         </is>
       </c>
     </row>
@@ -3891,17 +3896,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192C</t>
+          <t xml:space="preserve">IRL3276</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">62:56.960</t>
+          <t xml:space="preserve">60:20.760</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:56:56.640</t>
+          <t xml:space="preserve">20:00:20.760</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3911,7 +3916,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.480</t>
+          <t xml:space="preserve">9.340</t>
         </is>
       </c>
     </row>
@@ -3923,17 +3928,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">U4</t>
+          <t xml:space="preserve">ITA10767</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">63:43.030</t>
+          <t xml:space="preserve">66:54.930</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:57:43.770</t>
+          <t xml:space="preserve">20:06:54.930</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3943,7 +3948,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.490</t>
+          <t xml:space="preserve">9.345</t>
         </is>
       </c>
     </row>
@@ -3960,12 +3965,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">64:30.100</t>
+          <t xml:space="preserve">67:43.100</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:58:30.900</t>
+          <t xml:space="preserve">20:07:43.100</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3975,7 +3980,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.500</t>
+          <t xml:space="preserve">9.350</t>
         </is>
       </c>
     </row>
@@ -3987,17 +3992,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL216</t>
+          <t xml:space="preserve">1192C</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">65:17.170</t>
+          <t xml:space="preserve">69:54.270</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:59:17.030</t>
+          <t xml:space="preserve">20:09:54.270</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4007,7 +4012,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.510</t>
+          <t xml:space="preserve">9.355</t>
         </is>
       </c>
     </row>
@@ -4019,17 +4024,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">GK149</t>
+          <t xml:space="preserve">IRL5333</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">66:04.240</t>
+          <t xml:space="preserve">69:55.440</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:00:04.160</t>
+          <t xml:space="preserve">20:09:55.440</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4039,7 +4044,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.520</t>
+          <t xml:space="preserve">9.360</t>
         </is>
       </c>
     </row>
@@ -4051,17 +4056,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1844</t>
+          <t xml:space="preserve">GK149</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">66:51.310</t>
+          <t xml:space="preserve">70:01.610</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:00:51.290</t>
+          <t xml:space="preserve">20:10:01.610</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4071,7 +4076,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.530</t>
+          <t xml:space="preserve">9.365</t>
         </is>
       </c>
     </row>
@@ -4083,17 +4088,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">IRL8044</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">67:38.380</t>
+          <t xml:space="preserve">70:02.780</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:01:38.420</t>
+          <t xml:space="preserve">20:10:02.780</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4103,7 +4108,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.540</t>
+          <t xml:space="preserve">9.370</t>
         </is>
       </c>
     </row>
@@ -4115,17 +4120,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL21</t>
+          <t xml:space="preserve">U4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">68:25.450</t>
+          <t xml:space="preserve">70:09.950</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:02:25.550</t>
+          <t xml:space="preserve">20:10:09.950</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4135,7 +4140,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.550</t>
+          <t xml:space="preserve">9.375</t>
         </is>
       </c>
     </row>
@@ -4147,17 +4152,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2840</t>
+          <t xml:space="preserve">5499Y</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">69:12.520</t>
+          <t xml:space="preserve">70:12.120</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:03:12.680</t>
+          <t xml:space="preserve">20:10:12.120</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4167,7 +4172,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.560</t>
+          <t xml:space="preserve">9.380</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4189,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">69:59.590</t>
+          <t xml:space="preserve">70:43.290</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:03:59.810</t>
+          <t xml:space="preserve">20:10:43.290</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4199,7 +4204,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.570</t>
+          <t xml:space="preserve">9.385</t>
         </is>
       </c>
     </row>
@@ -4211,17 +4216,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2046</t>
+          <t xml:space="preserve">GBR6095T</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">70:46.660</t>
+          <t xml:space="preserve">70:48.460</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:04:46.940</t>
+          <t xml:space="preserve">20:10:48.460</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4231,7 +4236,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.580</t>
+          <t xml:space="preserve">9.390</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4248,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7887</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">71:33.730</t>
+          <t xml:space="preserve">71:12.630</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:05:33.070</t>
+          <t xml:space="preserve">20:11:12.630</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4263,7 +4268,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.590</t>
+          <t xml:space="preserve">9.395</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4280,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3429</t>
+          <t xml:space="preserve">IRL216</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">72:20.800</t>
+          <t xml:space="preserve">71:39.800</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:06:20.200</t>
+          <t xml:space="preserve">20:11:39.800</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4295,7 +4300,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.600</t>
+          <t xml:space="preserve">9.400</t>
         </is>
       </c>
     </row>
@@ -4307,17 +4312,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2237</t>
+          <t xml:space="preserve">IRL1844</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">73:07.870</t>
+          <t xml:space="preserve">72:10.970</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:07:07.330</t>
+          <t xml:space="preserve">20:12:10.970</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4327,7 +4332,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.610</t>
+          <t xml:space="preserve">9.405</t>
         </is>
       </c>
     </row>
@@ -4339,17 +4344,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL32032</t>
+          <t xml:space="preserve">IRL21</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">73:54.940</t>
+          <t xml:space="preserve">73:20.140</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:07:54.460</t>
+          <t xml:space="preserve">20:13:20.140</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4359,34 +4364,39 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.620</t>
+          <t xml:space="preserve">9.410</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">44.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7404</t>
+          <t xml:space="preserve">IRL2840</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">73:50.310</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">20:13:50.310</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">9.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.415</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4408,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4470</t>
+          <t xml:space="preserve">IRL2237</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4533,7 +4543,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:29</t>
+          <t xml:space="preserve">18:55</t>
         </is>
       </c>
     </row>
@@ -4592,175 +4602,175 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4475</t>
+          <t xml:space="preserve">IRL7887</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1759</t>
+          <t xml:space="preserve">IRL2046</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9216</t>
+          <t xml:space="preserve">IRL2237</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">KZ3494</t>
+          <t xml:space="preserve">IRL3429</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3330</t>
+          <t xml:space="preserve">IRL32032</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3300</t>
+          <t xml:space="preserve">IRL9855</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9202</t>
+          <t xml:space="preserve">IRL4076</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9992</t>
+          <t xml:space="preserve">IRL7404</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3214</t>
+          <t xml:space="preserve">IRL4240</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1551</t>
+          <t xml:space="preserve">GBR4947R</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1333</t>
+          <t xml:space="preserve">IRL2240</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9978</t>
+          <t xml:space="preserve">FRA78</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL33301</t>
+          <t xml:space="preserve">IRL4475</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5435</t>
+          <t xml:space="preserve">IRL4470</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL985</t>
+          <t xml:space="preserve">IRL35950</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4772,31 +4782,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3276</t>
+          <t xml:space="preserve">IRL1551</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITA10767</t>
+          <t xml:space="preserve">IRL9216</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5499Y</t>
+          <t xml:space="preserve">IRL1333</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4808,43 +4818,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5333</t>
+          <t xml:space="preserve">IRL985</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL8044</t>
+          <t xml:space="preserve">IRL9202</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR6095T</t>
+          <t xml:space="preserve">IRL3214</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192C</t>
+          <t xml:space="preserve">IRL9992</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4856,276 +4866,276 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">U4</t>
+          <t xml:space="preserve">IRL3330</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2480</t>
+          <t xml:space="preserve">IRL9978</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL216</t>
+          <t xml:space="preserve">IRL5435</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">GK149</t>
+          <t xml:space="preserve">KZ3494</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1844</t>
+          <t xml:space="preserve">IRL1759</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">IRL3300</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL21</t>
+          <t xml:space="preserve">IRL33301</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2840</t>
+          <t xml:space="preserve">IRL3276</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">148</t>
+          <t xml:space="preserve">ITA10767</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2046</t>
+          <t xml:space="preserve">IRL5333</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7887</t>
+          <t xml:space="preserve">GK149</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3429</t>
+          <t xml:space="preserve">GBR6095T</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2237</t>
+          <t xml:space="preserve">IRL8044</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL32032</t>
+          <t xml:space="preserve">1192C</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7404</t>
+          <t xml:space="preserve">IRL2480</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4470</t>
+          <t xml:space="preserve">U4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9855</t>
+          <t xml:space="preserve">IRL216</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">1.00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR4947R</t>
+          <t xml:space="preserve">148</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">4.00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4076</t>
+          <t xml:space="preserve">5499Y</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL35950</t>
+          <t xml:space="preserve">IRL2840</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2240</t>
+          <t xml:space="preserve">IRL1844</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">2.00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRA78</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.00</t>
+          <t xml:space="preserve">3.00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4240</t>
+          <t xml:space="preserve">IRL21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.00</t>
+          <t xml:space="preserve">6.00</t>
         </is>
       </c>
     </row>
@@ -5183,17 +5193,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4475</t>
+          <t xml:space="preserve">IRL7887</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">41:00.000</t>
+          <t xml:space="preserve">37:54.000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:40:00.000</t>
+          <t xml:space="preserve">19:37:54.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5215,17 +5225,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1759</t>
+          <t xml:space="preserve">IRL2046</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">41:47.070</t>
+          <t xml:space="preserve">41:23.170</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:40:47.130</t>
+          <t xml:space="preserve">19:41:23.170</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5235,7 +5245,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.210</t>
+          <t xml:space="preserve">9.205</t>
         </is>
       </c>
     </row>
@@ -5247,17 +5257,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9216</t>
+          <t xml:space="preserve">IRL2237</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">42:34.140</t>
+          <t xml:space="preserve">41:51.340</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:41:34.260</t>
+          <t xml:space="preserve">19:41:51.340</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5267,7 +5277,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.220</t>
+          <t xml:space="preserve">9.210</t>
         </is>
       </c>
     </row>
@@ -5279,17 +5289,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">KZ3494</t>
+          <t xml:space="preserve">IRL3429</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">43:21.210</t>
+          <t xml:space="preserve">42:03.510</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:42:21.390</t>
+          <t xml:space="preserve">19:42:03.510</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5299,7 +5309,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.230</t>
+          <t xml:space="preserve">9.215</t>
         </is>
       </c>
     </row>
@@ -5311,17 +5321,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3330</t>
+          <t xml:space="preserve">IRL32032</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">44:08.280</t>
+          <t xml:space="preserve">42:36.680</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:43:08.520</t>
+          <t xml:space="preserve">19:42:36.680</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5331,7 +5341,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.240</t>
+          <t xml:space="preserve">9.220</t>
         </is>
       </c>
     </row>
@@ -5343,17 +5353,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3300</t>
+          <t xml:space="preserve">IRL9855</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">44:55.350</t>
+          <t xml:space="preserve">44:03.850</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:43:55.650</t>
+          <t xml:space="preserve">19:44:03.850</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5363,7 +5373,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.250</t>
+          <t xml:space="preserve">9.225</t>
         </is>
       </c>
     </row>
@@ -5375,17 +5385,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9202</t>
+          <t xml:space="preserve">IRL4076</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">45:42.420</t>
+          <t xml:space="preserve">44:53.020</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:44:42.780</t>
+          <t xml:space="preserve">19:44:53.020</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5395,7 +5405,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.260</t>
+          <t xml:space="preserve">9.230</t>
         </is>
       </c>
     </row>
@@ -5407,17 +5417,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9992</t>
+          <t xml:space="preserve">IRL7404</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">46:29.490</t>
+          <t xml:space="preserve">44:54.190</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:45:29.910</t>
+          <t xml:space="preserve">19:44:54.190</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5427,7 +5437,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.270</t>
+          <t xml:space="preserve">9.235</t>
         </is>
       </c>
     </row>
@@ -5439,17 +5449,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3214</t>
+          <t xml:space="preserve">IRL4240</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">47:16.560</t>
+          <t xml:space="preserve">45:38.360</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:46:16.040</t>
+          <t xml:space="preserve">19:45:38.360</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5459,7 +5469,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.280</t>
+          <t xml:space="preserve">9.240</t>
         </is>
       </c>
     </row>
@@ -5471,17 +5481,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1551</t>
+          <t xml:space="preserve">GBR4947R</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">48:03.630</t>
+          <t xml:space="preserve">46:11.530</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:47:03.170</t>
+          <t xml:space="preserve">19:46:11.530</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5491,7 +5501,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.290</t>
+          <t xml:space="preserve">9.245</t>
         </is>
       </c>
     </row>
@@ -5503,17 +5513,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1333</t>
+          <t xml:space="preserve">IRL2240</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">48:50.700</t>
+          <t xml:space="preserve">46:17.700</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:47:50.300</t>
+          <t xml:space="preserve">19:46:17.700</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5523,7 +5533,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.300</t>
+          <t xml:space="preserve">9.250</t>
         </is>
       </c>
     </row>
@@ -5535,17 +5545,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9978</t>
+          <t xml:space="preserve">FRA78</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">49:37.770</t>
+          <t xml:space="preserve">46:37.870</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:48:37.430</t>
+          <t xml:space="preserve">19:46:37.870</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5555,7 +5565,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.310</t>
+          <t xml:space="preserve">9.255</t>
         </is>
       </c>
     </row>
@@ -5567,17 +5577,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL33301</t>
+          <t xml:space="preserve">IRL4475</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">50:24.840</t>
+          <t xml:space="preserve">46:54.040</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:49:24.560</t>
+          <t xml:space="preserve">19:46:54.040</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5587,7 +5597,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.320</t>
+          <t xml:space="preserve">9.260</t>
         </is>
       </c>
     </row>
@@ -5599,17 +5609,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5435</t>
+          <t xml:space="preserve">IRL4470</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">51:11.910</t>
+          <t xml:space="preserve">47:06.210</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:50:11.690</t>
+          <t xml:space="preserve">19:47:06.210</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5619,7 +5629,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.330</t>
+          <t xml:space="preserve">9.265</t>
         </is>
       </c>
     </row>
@@ -5631,17 +5641,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL985</t>
+          <t xml:space="preserve">IRL35950</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">51:58.980</t>
+          <t xml:space="preserve">48:09.380</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:50:58.820</t>
+          <t xml:space="preserve">19:48:09.380</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5651,7 +5661,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.340</t>
+          <t xml:space="preserve">9.270</t>
         </is>
       </c>
     </row>
@@ -5663,17 +5673,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3276</t>
+          <t xml:space="preserve">IRL1551</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">52:45.050</t>
+          <t xml:space="preserve">55:47.550</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:51:45.950</t>
+          <t xml:space="preserve">19:55:47.550</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5683,7 +5693,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.350</t>
+          <t xml:space="preserve">9.275</t>
         </is>
       </c>
     </row>
@@ -5695,17 +5705,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITA10767</t>
+          <t xml:space="preserve">IRL9216</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">53:32.120</t>
+          <t xml:space="preserve">56:14.720</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:52:32.080</t>
+          <t xml:space="preserve">19:56:14.720</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5715,7 +5725,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.360</t>
+          <t xml:space="preserve">9.280</t>
         </is>
       </c>
     </row>
@@ -5727,17 +5737,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5499Y</t>
+          <t xml:space="preserve">IRL1333</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">54:19.190</t>
+          <t xml:space="preserve">56:32.890</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:53:19.210</t>
+          <t xml:space="preserve">19:56:32.890</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5747,7 +5757,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.370</t>
+          <t xml:space="preserve">9.285</t>
         </is>
       </c>
     </row>
@@ -5759,17 +5769,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL5333</t>
+          <t xml:space="preserve">IRL985</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">55:06.260</t>
+          <t xml:space="preserve">57:07.060</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:54:06.340</t>
+          <t xml:space="preserve">19:57:07.060</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5779,7 +5789,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.380</t>
+          <t xml:space="preserve">9.290</t>
         </is>
       </c>
     </row>
@@ -5791,17 +5801,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL8044</t>
+          <t xml:space="preserve">IRL9202</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">55:53.330</t>
+          <t xml:space="preserve">57:34.230</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:54:53.470</t>
+          <t xml:space="preserve">19:57:34.230</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5811,7 +5821,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.390</t>
+          <t xml:space="preserve">9.295</t>
         </is>
       </c>
     </row>
@@ -5823,17 +5833,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR6095T</t>
+          <t xml:space="preserve">IRL3214</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">56:40.400</t>
+          <t xml:space="preserve">57:35.400</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:55:40.600</t>
+          <t xml:space="preserve">19:57:35.400</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5843,7 +5853,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.400</t>
+          <t xml:space="preserve">9.300</t>
         </is>
       </c>
     </row>
@@ -5855,17 +5865,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192C</t>
+          <t xml:space="preserve">IRL9992</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">57:27.470</t>
+          <t xml:space="preserve">57:40.570</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:56:27.730</t>
+          <t xml:space="preserve">19:57:40.570</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5875,7 +5885,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.410</t>
+          <t xml:space="preserve">9.305</t>
         </is>
       </c>
     </row>
@@ -5887,17 +5897,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">U4</t>
+          <t xml:space="preserve">IRL3330</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">58:14.540</t>
+          <t xml:space="preserve">57:51.740</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:57:14.860</t>
+          <t xml:space="preserve">19:57:51.740</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5907,7 +5917,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.420</t>
+          <t xml:space="preserve">9.310</t>
         </is>
       </c>
     </row>
@@ -5919,17 +5929,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2480</t>
+          <t xml:space="preserve">IRL9978</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">59:01.610</t>
+          <t xml:space="preserve">58:09.910</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:58:01.990</t>
+          <t xml:space="preserve">19:58:09.910</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5939,7 +5949,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.430</t>
+          <t xml:space="preserve">9.315</t>
         </is>
       </c>
     </row>
@@ -5951,17 +5961,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL216</t>
+          <t xml:space="preserve">IRL5435</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">59:48.680</t>
+          <t xml:space="preserve">58:11.080</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:58:48.120</t>
+          <t xml:space="preserve">19:58:11.080</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5971,7 +5981,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.440</t>
+          <t xml:space="preserve">9.320</t>
         </is>
       </c>
     </row>
@@ -5983,17 +5993,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">GK149</t>
+          <t xml:space="preserve">KZ3494</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">60:35.750</t>
+          <t xml:space="preserve">58:19.250</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">19:59:35.250</t>
+          <t xml:space="preserve">19:58:19.250</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6003,7 +6013,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.450</t>
+          <t xml:space="preserve">9.325</t>
         </is>
       </c>
     </row>
@@ -6015,17 +6025,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL1844</t>
+          <t xml:space="preserve">IRL1759</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">61:22.820</t>
+          <t xml:space="preserve">58:53.420</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:00:22.380</t>
+          <t xml:space="preserve">19:58:53.420</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6035,7 +6045,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.460</t>
+          <t xml:space="preserve">9.330</t>
         </is>
       </c>
     </row>
@@ -6047,17 +6057,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">IRL3300</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">62:09.890</t>
+          <t xml:space="preserve">58:53.590</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:01:09.510</t>
+          <t xml:space="preserve">19:58:53.590</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6067,7 +6077,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.470</t>
+          <t xml:space="preserve">9.335</t>
         </is>
       </c>
     </row>
@@ -6079,17 +6089,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL21</t>
+          <t xml:space="preserve">IRL33301</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">62:56.960</t>
+          <t xml:space="preserve">60:22.760</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:01:56.640</t>
+          <t xml:space="preserve">20:00:22.760</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6099,7 +6109,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.480</t>
+          <t xml:space="preserve">9.340</t>
         </is>
       </c>
     </row>
@@ -6111,17 +6121,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2840</t>
+          <t xml:space="preserve">IRL3276</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">63:43.030</t>
+          <t xml:space="preserve">61:01.930</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:02:43.770</t>
+          <t xml:space="preserve">20:01:01.930</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6131,7 +6141,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.490</t>
+          <t xml:space="preserve">9.345</t>
         </is>
       </c>
     </row>
@@ -6143,17 +6153,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">148</t>
+          <t xml:space="preserve">ITA10767</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">64:30.100</t>
+          <t xml:space="preserve">66:11.100</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:03:30.900</t>
+          <t xml:space="preserve">20:06:11.100</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6163,7 +6173,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.500</t>
+          <t xml:space="preserve">9.350</t>
         </is>
       </c>
     </row>
@@ -6175,17 +6185,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2046</t>
+          <t xml:space="preserve">IRL5333</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">65:17.170</t>
+          <t xml:space="preserve">68:12.270</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:04:17.030</t>
+          <t xml:space="preserve">20:08:12.270</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6195,7 +6205,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.510</t>
+          <t xml:space="preserve">9.355</t>
         </is>
       </c>
     </row>
@@ -6207,17 +6217,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7887</t>
+          <t xml:space="preserve">GK149</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">66:04.240</t>
+          <t xml:space="preserve">68:24.440</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:05:04.160</t>
+          <t xml:space="preserve">20:08:24.440</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6227,7 +6237,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.520</t>
+          <t xml:space="preserve">9.360</t>
         </is>
       </c>
     </row>
@@ -6239,17 +6249,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL3429</t>
+          <t xml:space="preserve">GBR6095T</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">66:51.310</t>
+          <t xml:space="preserve">69:08.610</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:05:51.290</t>
+          <t xml:space="preserve">20:09:08.610</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6259,7 +6269,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.530</t>
+          <t xml:space="preserve">9.365</t>
         </is>
       </c>
     </row>
@@ -6271,17 +6281,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2237</t>
+          <t xml:space="preserve">IRL8044</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">67:38.380</t>
+          <t xml:space="preserve">69:46.780</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:06:38.420</t>
+          <t xml:space="preserve">20:09:46.780</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6291,7 +6301,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.540</t>
+          <t xml:space="preserve">9.370</t>
         </is>
       </c>
     </row>
@@ -6303,17 +6313,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL32032</t>
+          <t xml:space="preserve">1192C</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">68:25.450</t>
+          <t xml:space="preserve">69:46.950</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:07:25.550</t>
+          <t xml:space="preserve">20:09:46.950</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6323,7 +6333,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.550</t>
+          <t xml:space="preserve">9.375</t>
         </is>
       </c>
     </row>
@@ -6335,17 +6345,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL7404</t>
+          <t xml:space="preserve">IRL2480</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">69:12.520</t>
+          <t xml:space="preserve">70:26.120</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:08:12.680</t>
+          <t xml:space="preserve">20:10:26.120</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6355,7 +6365,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.560</t>
+          <t xml:space="preserve">9.380</t>
         </is>
       </c>
     </row>
@@ -6367,17 +6377,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4470</t>
+          <t xml:space="preserve">U4</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">69:59.590</t>
+          <t xml:space="preserve">70:56.290</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:08:59.810</t>
+          <t xml:space="preserve">20:10:56.290</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6387,7 +6397,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.570</t>
+          <t xml:space="preserve">9.385</t>
         </is>
       </c>
     </row>
@@ -6399,17 +6409,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL9855</t>
+          <t xml:space="preserve">IRL216</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">70:46.660</t>
+          <t xml:space="preserve">71:11.460</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:09:46.940</t>
+          <t xml:space="preserve">20:11:11.460</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6419,7 +6429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.580</t>
+          <t xml:space="preserve">9.390</t>
         </is>
       </c>
     </row>
@@ -6431,17 +6441,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBR4947R</t>
+          <t xml:space="preserve">148</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">71:33.730</t>
+          <t xml:space="preserve">71:39.630</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:10:33.070</t>
+          <t xml:space="preserve">20:11:39.630</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6451,7 +6461,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.590</t>
+          <t xml:space="preserve">9.395</t>
         </is>
       </c>
     </row>
@@ -6463,17 +6473,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4076</t>
+          <t xml:space="preserve">5499Y</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">72:20.800</t>
+          <t xml:space="preserve">71:53.800</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:11:20.200</t>
+          <t xml:space="preserve">20:11:53.800</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6483,7 +6493,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.600</t>
+          <t xml:space="preserve">9.400</t>
         </is>
       </c>
     </row>
@@ -6495,17 +6505,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL35950</t>
+          <t xml:space="preserve">IRL2840</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">73:07.870</t>
+          <t xml:space="preserve">72:36.970</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:12:07.330</t>
+          <t xml:space="preserve">20:12:36.970</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6515,7 +6525,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.610</t>
+          <t xml:space="preserve">9.405</t>
         </is>
       </c>
     </row>
@@ -6527,17 +6537,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL2240</t>
+          <t xml:space="preserve">IRL1844</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">73:54.940</t>
+          <t xml:space="preserve">72:37.140</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">20:12:54.460</t>
+          <t xml:space="preserve">20:12:37.140</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6547,34 +6557,39 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.620</t>
+          <t xml:space="preserve">9.410</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">44.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRA78</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">73:03.310</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">20:13:03.310</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">---</t>
+          <t xml:space="preserve">9.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.415</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6601,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRL4240</t>
+          <t xml:space="preserve">IRL21</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6721,12 +6736,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">39.</t>
+          <t xml:space="preserve">1.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">32.</t>
+          <t xml:space="preserve">2.</t>
         </is>
       </c>
     </row>
@@ -6738,17 +6753,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40.</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.</t>
+          <t xml:space="preserve">1.</t>
         </is>
       </c>
     </row>
@@ -6760,17 +6775,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t xml:space="preserve">2.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t xml:space="preserve">3.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41.</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.</t>
+          <t xml:space="preserve">4.</t>
         </is>
       </c>
     </row>
@@ -6782,17 +6797,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.</t>
+          <t xml:space="preserve">5.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">42.</t>
+          <t xml:space="preserve">DNF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.</t>
+          <t xml:space="preserve">3.</t>
         </is>
       </c>
     </row>
@@ -6804,17 +6819,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t xml:space="preserve">3.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t xml:space="preserve">5.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36.</t>
         </is>
       </c>
     </row>
@@ -6831,12 +6846,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">5.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.</t>
+          <t xml:space="preserve">8.</t>
         </is>
       </c>
     </row>
@@ -6848,17 +6863,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.</t>
+          <t xml:space="preserve">15.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">12.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">38.</t>
+          <t xml:space="preserve">14.</t>
         </is>
       </c>
     </row>
@@ -6870,17 +6885,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.</t>
+          <t xml:space="preserve">7.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.</t>
+          <t xml:space="preserve">10.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39.</t>
+          <t xml:space="preserve">6.</t>
         </is>
       </c>
     </row>
@@ -6892,17 +6907,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.</t>
+          <t xml:space="preserve">12.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.</t>
+          <t xml:space="preserve">11.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.</t>
+          <t xml:space="preserve">10.</t>
         </is>
       </c>
     </row>
@@ -6914,17 +6929,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.</t>
+          <t xml:space="preserve">9.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.</t>
+          <t xml:space="preserve">9.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41.</t>
+          <t xml:space="preserve">7.</t>
         </is>
       </c>
     </row>
@@ -6936,17 +6951,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.</t>
+          <t xml:space="preserve">13.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.</t>
+          <t xml:space="preserve">13.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">42.</t>
+          <t xml:space="preserve">15.</t>
         </is>
       </c>
     </row>
@@ -6958,17 +6973,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.</t>
+          <t xml:space="preserve">8.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.</t>
+          <t xml:space="preserve">6.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.</t>
+          <t xml:space="preserve">11.</t>
         </is>
       </c>
     </row>
@@ -6980,17 +6995,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.</t>
+          <t xml:space="preserve">10.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.</t>
+          <t xml:space="preserve">8.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">12.</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7027,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">9.</t>
         </is>
       </c>
     </row>
@@ -7024,17 +7039,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.</t>
+          <t xml:space="preserve">11.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.</t>
+          <t xml:space="preserve">14.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.</t>
+          <t xml:space="preserve">13.</t>
         </is>
       </c>
     </row>
@@ -7046,17 +7061,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.</t>
+          <t xml:space="preserve">24.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.</t>
+          <t xml:space="preserve">27.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.</t>
+          <t xml:space="preserve">27.</t>
         </is>
       </c>
     </row>
@@ -7068,17 +7083,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t xml:space="preserve">20.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t xml:space="preserve">17.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.</t>
         </is>
       </c>
     </row>
@@ -7090,17 +7105,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.</t>
+          <t xml:space="preserve">27.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.</t>
+          <t xml:space="preserve">23.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.</t>
+          <t xml:space="preserve">26.</t>
         </is>
       </c>
     </row>
@@ -7112,17 +7127,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.</t>
+          <t xml:space="preserve">18.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.</t>
+          <t xml:space="preserve">17.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.</t>
+          <t xml:space="preserve">23.</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7149,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.</t>
+          <t xml:space="preserve">28.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.</t>
+          <t xml:space="preserve">22.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.</t>
+          <t xml:space="preserve">28.</t>
         </is>
       </c>
     </row>
@@ -7156,17 +7171,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.</t>
+          <t xml:space="preserve">29.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.</t>
+          <t xml:space="preserve">20.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.</t>
+          <t xml:space="preserve">20.</t>
         </is>
       </c>
     </row>
@@ -7178,17 +7193,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t xml:space="preserve">26.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t xml:space="preserve">22.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8.</t>
         </is>
       </c>
     </row>
@@ -7200,17 +7215,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.</t>
+          <t xml:space="preserve">16.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.</t>
+          <t xml:space="preserve">26.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.</t>
+          <t xml:space="preserve">21.</t>
         </is>
       </c>
     </row>
@@ -7222,17 +7237,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.</t>
+          <t xml:space="preserve">19.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.</t>
+          <t xml:space="preserve">16.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.</t>
+          <t xml:space="preserve">16.</t>
         </is>
       </c>
     </row>
@@ -7244,17 +7259,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.</t>
+          <t xml:space="preserve">23.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t xml:space="preserve">19.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t xml:space="preserve">18.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.</t>
         </is>
       </c>
     </row>
@@ -7266,17 +7281,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">26.</t>
+          <t xml:space="preserve">25.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.</t>
+          <t xml:space="preserve">25.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.</t>
+          <t xml:space="preserve">24.</t>
         </is>
       </c>
     </row>
@@ -7288,17 +7303,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.</t>
+          <t xml:space="preserve">22.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.</t>
+          <t xml:space="preserve">28.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.</t>
+          <t xml:space="preserve">29.</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7325,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.</t>
+          <t xml:space="preserve">21.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7320,7 +7335,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.</t>
+          <t xml:space="preserve">25.</t>
         </is>
       </c>
     </row>
@@ -7332,17 +7347,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.</t>
+          <t xml:space="preserve">17.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.</t>
+          <t xml:space="preserve">18.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.</t>
+          <t xml:space="preserve">19.</t>
         </is>
       </c>
     </row>
@@ -7359,12 +7374,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.</t>
+          <t xml:space="preserve">29.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.</t>
+          <t xml:space="preserve">30.</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7396,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.</t>
+          <t xml:space="preserve">30.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">17.</t>
+          <t xml:space="preserve">31.</t>
         </is>
       </c>
     </row>
@@ -7398,17 +7413,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">32.</t>
+          <t xml:space="preserve">35.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.</t>
+          <t xml:space="preserve">37.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.</t>
+          <t xml:space="preserve">41.</t>
         </is>
       </c>
     </row>
@@ -7420,17 +7435,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t xml:space="preserve">37.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t xml:space="preserve">33.</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26.</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.</t>
+          <t xml:space="preserve">32.</t>
         </is>
       </c>
     </row>
@@ -7442,17 +7457,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.</t>
+          <t xml:space="preserve">36.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.</t>
+          <t xml:space="preserve">35.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.</t>
+          <t xml:space="preserve">35.</t>
         </is>
       </c>
     </row>
@@ -7464,17 +7479,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.</t>
+          <t xml:space="preserve">40.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.</t>
+          <t xml:space="preserve">39.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.</t>
+          <t xml:space="preserve">34.</t>
         </is>
       </c>
     </row>
@@ -7486,17 +7501,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t xml:space="preserve">33.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t xml:space="preserve">36.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22.</t>
         </is>
       </c>
     </row>
@@ -7508,17 +7523,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.</t>
+          <t xml:space="preserve">44.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.</t>
+          <t xml:space="preserve">36.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">23.</t>
+          <t xml:space="preserve">38.</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7545,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">38.</t>
+          <t xml:space="preserve">32.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7540,7 +7555,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.</t>
+          <t xml:space="preserve">37.</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7572,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">32.</t>
+          <t xml:space="preserve">41.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.</t>
+          <t xml:space="preserve">39.</t>
         </is>
       </c>
     </row>
@@ -7574,17 +7589,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.</t>
+          <t xml:space="preserve">34.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t xml:space="preserve">34.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t xml:space="preserve">33.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26.</t>
         </is>
       </c>
     </row>
@@ -7596,17 +7611,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">41.</t>
+          <t xml:space="preserve">42.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.</t>
+          <t xml:space="preserve">42.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">27.</t>
+          <t xml:space="preserve">43.</t>
         </is>
       </c>
     </row>
@@ -7618,17 +7633,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">42.</t>
+          <t xml:space="preserve">43.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.</t>
+          <t xml:space="preserve">40.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.</t>
+          <t xml:space="preserve">44.</t>
         </is>
       </c>
     </row>
@@ -7640,17 +7655,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t xml:space="preserve">45.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t xml:space="preserve">43.</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36.</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.</t>
+          <t xml:space="preserve">DNF</t>
         </is>
       </c>
     </row>
@@ -7662,17 +7677,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">41.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.</t>
+          <t xml:space="preserve">44.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.</t>
+          <t xml:space="preserve">42.</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7699,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">DNF</t>
+          <t xml:space="preserve">38.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7694,7 +7709,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.</t>
+          <t xml:space="preserve">40.</t>
         </is>
       </c>
     </row>
